--- a/002_SapAriba_Mars_Dispatcher/lib/net45/Data/Config.xlsx
+++ b/002_SapAriba_Mars_Dispatcher/lib/net45/Data/Config.xlsx
@@ -2304,8 +2304,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010039B5D92226A63A4AA91620FECE37D35A" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d40255432343d9758207c18648e5a326">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c4012d6b-a91c-4ec0-90d0-0537ad76586d" xmlns:ns3="ef49ae6b-e58c-46b9-9be1-3da75242d3af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c599fead97c0ca65b033184e8fb5180a" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010039B5D92226A63A4AA91620FECE37D35A" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bdbcd375e0c7d3bbebf91d046ff7fb08">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c4012d6b-a91c-4ec0-90d0-0537ad76586d" xmlns:ns3="ef49ae6b-e58c-46b9-9be1-3da75242d3af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a66cef3a897516cec54955f0a6fb6ea9" ns2:_="" ns3:_="">
     <xsd:import namespace="c4012d6b-a91c-4ec0-90d0-0537ad76586d"/>
     <xsd:import namespace="ef49ae6b-e58c-46b9-9be1-3da75242d3af"/>
     <xsd:element name="properties">
@@ -2325,6 +2325,8 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2375,6 +2377,16 @@
       </xsd:complexType>
     </xsd:element>
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="19" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="21" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -2541,7 +2553,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4CC0547-7F87-4CDD-A7E1-4F697B2F79A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{536C73B9-D3AB-4242-B991-E4EA65BEADD2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
